--- a/Santarin_Ex3A_tables.xlsx
+++ b/Santarin_Ex3A_tables.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marenzasantarin\OneDrive - Year Up- BOS\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F6594E-71DC-4709-AA8C-F876981B2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4140B96D-74D0-4AC7-B362-03D2D47745E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{11E1D229-2137-46FE-97F3-3E671B5A1F80}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{11E1D229-2137-46FE-97F3-3E671B5A1F80}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
-    <sheet name="Dogs" sheetId="2" r:id="rId2"/>
-    <sheet name="Walkers" sheetId="3" r:id="rId3"/>
+    <sheet name="Walkers" sheetId="3" r:id="rId2"/>
+    <sheet name="Dogs" sheetId="2" r:id="rId3"/>
     <sheet name="Walks" sheetId="4" r:id="rId4"/>
     <sheet name="Payments" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>customer_id</t>
   </si>
@@ -100,16 +100,73 @@
   </si>
   <si>
     <t>payment_method</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Ignacio</t>
+  </si>
+  <si>
+    <t>619-751-9122</t>
+  </si>
+  <si>
+    <t>janignacio@email.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124 Conch Street, Bikini Bottom </t>
+  </si>
+  <si>
+    <t>Julius</t>
+  </si>
+  <si>
+    <t>Ramos</t>
+  </si>
+  <si>
+    <t>619-344-2371</t>
+  </si>
+  <si>
+    <t>jramos@email.com</t>
+  </si>
+  <si>
+    <t>Bumi</t>
+  </si>
+  <si>
+    <t>Dachshund</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Card</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -144,10 +201,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -157,8 +215,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -491,13 +561,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDB729F-2AF9-4E05-A35D-3CA19954FC8C}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="15.6328125" style="4"/>
+    <col min="1" max="4" width="15.6328125" style="4"/>
+    <col min="5" max="5" width="19.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="15.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -513,65 +586,131 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="10">
+        <v>101</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{EA51EE25-EA9B-4297-B543-3EF948B34CAF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18771DD-7173-4F43-8FC0-565E0240FCD5}">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CA076-7FE5-419E-899A-5515389D8B43}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="16.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>201</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{D7EDA241-7804-402E-8F20-99704CDC7B68}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CA076-7FE5-419E-899A-5515389D8B43}">
-  <dimension ref="A1:E1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18771DD-7173-4F43-8FC0-565E0240FCD5}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>301</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="9">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="9">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -581,7 +720,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3905CD-46EE-48B4-9B28-A384FB471E59}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -605,6 +744,29 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>401</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46113</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.625</v>
+      </c>
+      <c r="D2" s="9">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="9">
+        <v>301</v>
+      </c>
+      <c r="G2" s="9">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -614,7 +776,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C396F9-B5C3-46DC-8EBC-3E2E9D665B8C}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -637,6 +799,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>501</v>
+      </c>
+      <c r="B2" s="8">
+        <v>40</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="9">
+        <v>401</v>
+      </c>
+      <c r="F2" s="9">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
